--- a/docs/files/REPORT_FILTRI/RZV - BRUNI ANGELO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - BRUNI ANGELO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>14</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>324</v>
+        <v>454</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>266</v>
+        <v>378</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,28 +821,28 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>113</v>
+        <v>164</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>0</v>
@@ -856,12 +856,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>09237</t>
+          <t>09119</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>SAN SEVERO</t>
+          <t>BARI</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -871,51 +871,51 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>CASCIANI GABRIELE</t>
+          <t>RENNA MARCO</t>
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>36</v>
+        <v>86</v>
       </c>
       <c r="G12" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="H12" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="I12" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="J12" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="H12" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="I12" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="J12" s="12" t="n">
-        <v>7</v>
-      </c>
       <c r="K12" s="12" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>09119</t>
+          <t>09139</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>BARI</t>
+          <t>CASAMASSIMA</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -925,51 +925,51 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>RENNA MARCO</t>
+          <t>TESORO DAVIDE</t>
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>09139</t>
+          <t>09237</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CASAMASSIMA</t>
+          <t>SAN SEVERO</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -979,35 +979,35 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>TESORO DAVIDE</t>
+          <t>CASCIANI GABRIELE</t>
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1037,28 +1037,28 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="G15" s="12" t="n">
         <v>3</v>
       </c>
       <c r="H15" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I15" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="J15" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I15" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="J15" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="K15" s="12" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>0</v>
@@ -1091,35 +1091,35 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>4</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>0</v>
@@ -1157,16 +1157,16 @@
         <v>0</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>0</v>
@@ -1202,13 +1202,13 @@
         <v>15</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I18" s="12" t="n">
         <v>11</v>
@@ -1220,26 +1220,26 @@
         <v>5</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>09267</t>
+          <t>38047</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>LESINA</t>
+          <t>BARI</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1249,14 +1249,14 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>CASCIANI GABRIELE</t>
+          <t>RENNA MARCO</t>
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="G19" s="12" t="n">
         <v>1</v>
@@ -1265,35 +1265,35 @@
         <v>0</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>09424</t>
+          <t>09267</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>MASSAFRA</t>
+          <t>LESINA</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1303,32 +1303,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>TESORO DAVIDE</t>
+          <t>CASCIANI GABRIELE</t>
         </is>
       </c>
       <c r="E20" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="F20" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="G20" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="F20" s="12" t="n">
-        <v>29</v>
-      </c>
-      <c r="G20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="I20" s="12" t="n">
+      <c r="J20" s="12" t="n">
         <v>3</v>
-      </c>
-      <c r="J20" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="K20" s="12" t="n">
         <v>5</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>0</v>
@@ -1342,12 +1342,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>38047</t>
+          <t>09424</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>BARI</t>
+          <t>MASSAFRA</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1357,32 +1357,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>RENNA MARCO</t>
+          <t>TESORO DAVIDE</t>
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="G21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>0</v>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>0</v>
@@ -1433,17 +1433,17 @@
         <v>0</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1490,14 +1490,14 @@
         <v>0</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/RZV - BRUNI ANGELO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - BRUNI ANGELO.xlsx
@@ -535,7 +535,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -899,7 +899,7 @@
         <v>60</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>0.03333333333333333</v>
+        <v>2</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>23</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>0.4347826086956522</v>
+        <v>10</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>54</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>0.1666666666666667</v>
+        <v>9</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>

--- a/docs/files/REPORT_FILTRI/RZV - BRUNI ANGELO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - BRUNI ANGELO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>14</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>454</v>
+        <v>483</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>378</v>
+        <v>401</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,47 +821,47 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="F11" s="12" t="n">
         <v>38</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H11" s="12" t="n">
         <v>12</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>09119</t>
+          <t>09237</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>BARI</t>
+          <t>SAN SEVERO</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -871,35 +871,35 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>RENNA MARCO</t>
+          <t>CASCIANI GABRIELE</t>
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -910,12 +910,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>09139</t>
+          <t>09119</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>CASAMASSIMA</t>
+          <t>BARI</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -925,51 +925,51 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>TESORO DAVIDE</t>
+          <t>RENNA MARCO</t>
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>45</v>
+        <v>88</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>09237</t>
+          <t>09139</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>SAN SEVERO</t>
+          <t>CASAMASSIMA</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -979,35 +979,35 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>CASCIANI GABRIELE</t>
+          <t>TESORO DAVIDE</t>
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1037,35 +1037,35 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G15" s="12" t="n">
         <v>3</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J15" s="12" t="n">
         <v>3</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1091,28 +1091,28 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>0</v>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>0</v>
@@ -1157,7 +1157,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J17" s="12" t="n">
         <v>5</v>
@@ -1173,19 +1173,19 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>09242</t>
+          <t>09267</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI ROTONDO</t>
+          <t>LESINA</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1199,47 +1199,47 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I18" s="12" t="n">
         <v>11</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>38047</t>
+          <t>09242</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>BARI</t>
+          <t>SAN GIOVANNI ROTONDO</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1249,51 +1249,51 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>RENNA MARCO</t>
+          <t>CASCIANI GABRIELE</t>
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I19" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="J19" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="J19" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="K19" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>09267</t>
+          <t>38047</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>LESINA</t>
+          <t>BARI</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1303,39 +1303,39 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>CASCIANI GABRIELE</t>
+          <t>RENNA MARCO</t>
         </is>
       </c>
       <c r="E20" s="12" t="n">
         <v>14</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
         <v>12</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="G21" s="12" t="n">
         <v>0</v>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
         <v>0</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - BRUNI ANGELO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - BRUNI ANGELO.xlsx
@@ -525,7 +525,7 @@
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1512,7 +1512,11 @@
           <t>LUCERA</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
           <t>CASCIANI GABRIELE</t>

--- a/docs/files/REPORT_FILTRI/RZV - BRUNI ANGELO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - BRUNI ANGELO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>14</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>483</v>
+        <v>520</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>401</v>
+        <v>435</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,28 +821,28 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>178</v>
+        <v>200</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="H11" s="12" t="n">
         <v>12</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>12</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>0</v>
@@ -856,12 +856,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>09237</t>
+          <t>09119</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>SAN SEVERO</t>
+          <t>BARI</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -871,35 +871,35 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>CASCIANI GABRIELE</t>
+          <t>RENNA MARCO</t>
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -910,12 +910,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>09119</t>
+          <t>09237</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>BARI</t>
+          <t>SAN SEVERO</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -925,35 +925,35 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>RENNA MARCO</t>
+          <t>CASCIANI GABRIELE</t>
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="L13" s="12" t="n">
         <v>62</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -983,10 +983,10 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G14" s="12" t="n">
         <v>4</v>
@@ -995,23 +995,23 @@
         <v>3</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>11</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>11</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1037,35 +1037,35 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="G15" s="12" t="n">
         <v>3</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J15" s="12" t="n">
         <v>3</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
         <v>34</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G16" s="12" t="n">
         <v>3</v>
@@ -1112,7 +1112,7 @@
         <v>5</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>0</v>
@@ -1145,25 +1145,25 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L17" s="12" t="n">
         <v>3</v>
@@ -1234,12 +1234,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>09242</t>
+          <t>38047</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI ROTONDO</t>
+          <t>BARI</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1249,51 +1249,51 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>CASCIANI GABRIELE</t>
+          <t>RENNA MARCO</t>
         </is>
       </c>
       <c r="E19" s="12" t="n">
         <v>15</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>38047</t>
+          <t>09242</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>BARI</t>
+          <t>SAN GIOVANNI ROTONDO</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1303,39 +1303,39 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>RENNA MARCO</t>
+          <t>CASCIANI GABRIELE</t>
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
         <v>1</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - BRUNI ANGELO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - BRUNI ANGELO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>14</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>520</v>
+        <v>581</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>435</v>
+        <v>487</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,28 +821,28 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>200</v>
+        <v>233</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="H11" s="12" t="n">
         <v>12</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>192</v>
+        <v>224</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>0</v>
@@ -856,12 +856,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>09119</t>
+          <t>09139</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>BARI</t>
+          <t>CASAMASSIMA</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -871,39 +871,39 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>RENNA MARCO</t>
+          <t>TESORO DAVIDE</t>
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G13" s="12" t="n">
         <v>10</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="J13" s="12" t="n">
         <v>13</v>
@@ -950,7 +950,7 @@
         <v>9</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>9</v>
@@ -964,12 +964,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>09139</t>
+          <t>09119</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CASAMASSIMA</t>
+          <t>BARI</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -979,39 +979,39 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>TESORO DAVIDE</t>
+          <t>RENNA MARCO</t>
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1037,35 +1037,35 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="J15" s="12" t="n">
         <v>3</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1091,28 +1091,28 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>0</v>
@@ -1145,19 +1145,19 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="H17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="12" t="n">
         <v>27</v>
-      </c>
-      <c r="F17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="12" t="n">
-        <v>22</v>
       </c>
       <c r="J17" s="12" t="n">
         <v>6</v>
@@ -1199,10 +1199,10 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>1</v>
@@ -1211,10 +1211,10 @@
         <v>0</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>6</v>
@@ -1253,19 +1253,19 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J19" s="12" t="n">
         <v>2</v>
@@ -1310,7 +1310,7 @@
         <v>15</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - BRUNI ANGELO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - BRUNI ANGELO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>14</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>581</v>
+        <v>602</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>487</v>
+        <v>504</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,47 +821,47 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>13</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>09139</t>
+          <t>09237</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>CASAMASSIMA</t>
+          <t>SAN SEVERO</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -871,51 +871,51 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>TESORO DAVIDE</t>
+          <t>CASCIANI GABRIELE</t>
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>55</v>
+        <v>96</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>09237</t>
+          <t>09119</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>SAN SEVERO</t>
+          <t>BARI</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -925,35 +925,35 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>CASCIANI GABRIELE</t>
+          <t>RENNA MARCO</t>
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -964,12 +964,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>09119</t>
+          <t>09139</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>BARI</t>
+          <t>CASAMASSIMA</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -979,39 +979,39 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>RENNA MARCO</t>
+          <t>TESORO DAVIDE</t>
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1040,7 @@
         <v>49</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G15" s="12" t="n">
         <v>4</v>
@@ -1058,14 +1058,14 @@
         <v>21</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1091,28 +1091,28 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G16" s="12" t="n">
         <v>4</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>0</v>
@@ -1145,35 +1145,35 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>4</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1202,13 +1202,13 @@
         <v>18</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" s="12" t="n">
         <v>12</v>
@@ -1274,14 +1274,14 @@
         <v>2</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1364,13 +1364,13 @@
         <v>12</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I21" s="12" t="n">
         <v>5</v>

--- a/docs/files/REPORT_FILTRI/RZV - BRUNI ANGELO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - BRUNI ANGELO.xlsx
@@ -1512,11 +1512,7 @@
           <t>LUCERA</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
+      <c r="C24" s="2" t="inlineStr"/>
       <c r="D24" s="2" t="inlineStr">
         <is>
           <t>CASCIANI GABRIELE</t>

--- a/docs/files/REPORT_FILTRI/RZV - BRUNI ANGELO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - BRUNI ANGELO.xlsx
@@ -209,23 +209,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N24" headerRowCount="1">
-  <autoFilter ref="A10:N24"/>
-  <tableColumns count="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O24" headerRowCount="1">
+  <autoFilter ref="A10:O24"/>
+  <tableColumns count="15">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
-    <tableColumn id="3" name="Agente"/>
-    <tableColumn id="4" name="CR"/>
-    <tableColumn id="5" name="Vend 2026"/>
-    <tableColumn id="6" name="Vend 2025"/>
-    <tableColumn id="7" name="Ass 2026"/>
-    <tableColumn id="8" name="Ass 2025"/>
-    <tableColumn id="9" name="Prospect"/>
-    <tableColumn id="10" name="Twin"/>
-    <tableColumn id="11" name="Business"/>
-    <tableColumn id="12" name="Sost anno"/>
-    <tableColumn id="13" name="UP EU"/>
-    <tableColumn id="14" name="Stato"/>
+    <tableColumn id="3" name="Indirizzo"/>
+    <tableColumn id="4" name="Agente"/>
+    <tableColumn id="5" name="CR"/>
+    <tableColumn id="6" name="Vend 2026"/>
+    <tableColumn id="7" name="Vend 2025"/>
+    <tableColumn id="8" name="Ass 2026"/>
+    <tableColumn id="9" name="Ass 2025"/>
+    <tableColumn id="10" name="Prospect"/>
+    <tableColumn id="11" name="Twin"/>
+    <tableColumn id="12" name="Business"/>
+    <tableColumn id="13" name="Sost anno"/>
+    <tableColumn id="14" name="UP EU"/>
+    <tableColumn id="15" name="Stato"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -520,23 +521,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N24"/>
+  <dimension ref="A1:O24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -558,6 +560,7 @@
       <c r="L1" s="2" t="n"/>
       <c r="M1" s="2" t="n"/>
       <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n"/>
@@ -574,6 +577,7 @@
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="n"/>
       <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -598,6 +602,7 @@
       <c r="L3" s="2" t="n"/>
       <c r="M3" s="2" t="n"/>
       <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -622,6 +627,7 @@
       <c r="L4" s="2" t="n"/>
       <c r="M4" s="2" t="n"/>
       <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n"/>
@@ -638,6 +644,7 @@
       <c r="L5" s="2" t="n"/>
       <c r="M5" s="2" t="n"/>
       <c r="N5" s="2" t="n"/>
+      <c r="O5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -670,6 +677,7 @@
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
       <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -694,6 +702,7 @@
       <c r="L7" s="2" t="n"/>
       <c r="M7" s="2" t="n"/>
       <c r="N7" s="2" t="n"/>
+      <c r="O7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
@@ -710,6 +719,7 @@
       <c r="L8" s="2" t="n"/>
       <c r="M8" s="2" t="n"/>
       <c r="N8" s="2" t="n"/>
+      <c r="O8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
@@ -726,6 +736,7 @@
       <c r="L9" s="2" t="n"/>
       <c r="M9" s="2" t="n"/>
       <c r="N9" s="2" t="n"/>
+      <c r="O9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
@@ -740,60 +751,65 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
+          <t>Indirizzo</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
           <t>Agente</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>CR</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>Vend 2026</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>Vend 2025</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>Ass 2026</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
         <is>
           <t>Ass 2025</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="K10" s="11" t="inlineStr">
         <is>
           <t>Twin</t>
         </is>
       </c>
-      <c r="K10" s="11" t="inlineStr">
+      <c r="L10" s="11" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="L10" s="11" t="inlineStr">
+      <c r="M10" s="11" t="inlineStr">
         <is>
           <t>Sost anno</t>
         </is>
       </c>
-      <c r="M10" s="11" t="inlineStr">
+      <c r="N10" s="11" t="inlineStr">
         <is>
           <t>UP EU</t>
         </is>
       </c>
-      <c r="N10" s="11" t="inlineStr">
+      <c r="O10" s="11" t="inlineStr">
         <is>
           <t>Stato</t>
         </is>
@@ -812,42 +828,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>SS ADRIATICA KM 838+890</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
           <t>Cali Giuseppe</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>TEDONE VITO</t>
         </is>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="F11" s="12" t="n">
         <v>241</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="G11" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="H11" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="H11" s="12" t="n">
+      <c r="I11" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="I11" s="12" t="n">
+      <c r="J11" s="12" t="n">
         <v>232</v>
       </c>
-      <c r="J11" s="12" t="n">
+      <c r="K11" s="12" t="n">
         <v>88</v>
       </c>
-      <c r="K11" s="12" t="n">
+      <c r="L11" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="L11" s="12" t="n">
+      <c r="M11" s="12" t="n">
         <v>70</v>
       </c>
-      <c r="M11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -866,42 +887,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>VIA GIUSTINO FORTUNATO SNC</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>Cali Giuseppe</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>CASCIANI GABRIELE</t>
         </is>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="F12" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="G12" s="12" t="n">
         <v>96</v>
       </c>
-      <c r="G12" s="12" t="n">
+      <c r="H12" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="H12" s="12" t="n">
+      <c r="I12" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I12" s="12" t="n">
+      <c r="J12" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="J12" s="12" t="n">
+      <c r="K12" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="K12" s="12" t="n">
+      <c r="L12" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="L12" s="12" t="n">
+      <c r="M12" s="12" t="n">
         <v>68</v>
       </c>
-      <c r="M12" s="12" t="n">
+      <c r="N12" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -920,42 +946,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>VIA BITRITTO KM 4+197</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>Cali Giuseppe</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>RENNA MARCO</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="F13" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="G13" s="12" t="n">
         <v>95</v>
       </c>
-      <c r="G13" s="12" t="n">
+      <c r="H13" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="H13" s="12" t="n">
+      <c r="I13" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="I13" s="12" t="n">
+      <c r="J13" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="J13" s="12" t="n">
+      <c r="K13" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="K13" s="12" t="n">
+      <c r="L13" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="L13" s="12" t="n">
+      <c r="M13" s="12" t="n">
         <v>70</v>
       </c>
-      <c r="M13" s="12" t="n">
+      <c r="N13" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -974,42 +1005,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>S.S. 100 KM. 20+123</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
           <t>Cali Giuseppe</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>TESORO DAVIDE</t>
         </is>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="F14" s="12" t="n">
         <v>56</v>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="G14" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="G14" s="12" t="n">
+      <c r="H14" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="H14" s="12" t="n">
+      <c r="I14" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I14" s="12" t="n">
+      <c r="J14" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="J14" s="12" t="n">
+      <c r="K14" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="K14" s="12" t="n">
+      <c r="L14" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="L14" s="12" t="n">
+      <c r="M14" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="M14" s="12" t="n">
+      <c r="N14" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1028,42 +1064,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>BRUNO BUOZZI N</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
           <t>Cali Giuseppe</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>RENNA MARCO</t>
         </is>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="F15" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="G15" s="12" t="n">
         <v>62</v>
       </c>
-      <c r="G15" s="12" t="n">
+      <c r="H15" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="H15" s="12" t="n">
+      <c r="I15" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="I15" s="12" t="n">
+      <c r="J15" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="J15" s="12" t="n">
+      <c r="K15" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K15" s="12" t="n">
+      <c r="L15" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="L15" s="12" t="n">
+      <c r="M15" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="M15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="N15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1082,42 +1123,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>VIALE DEGLI AVIATORI 108/B</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>Cali Giuseppe</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>CASCIANI GABRIELE</t>
         </is>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="F16" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="G16" s="12" t="n">
         <v>77</v>
       </c>
-      <c r="G16" s="12" t="n">
+      <c r="H16" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="H16" s="12" t="n">
+      <c r="I16" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I16" s="12" t="n">
+      <c r="J16" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="J16" s="12" t="n">
+      <c r="K16" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="K16" s="12" t="n">
+      <c r="L16" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L16" s="12" t="n">
+      <c r="M16" s="12" t="n">
         <v>79</v>
       </c>
-      <c r="M16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="N16" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1136,42 +1182,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>LOCALITA' FANTINA</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
           <t>Cali Giuseppe</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>CASCIANI GABRIELE</t>
         </is>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="F17" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="F17" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="H17" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="J17" s="12" t="n">
+      <c r="K17" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="K17" s="12" t="n">
+      <c r="L17" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="L17" s="12" t="n">
+      <c r="M17" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="M17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="N17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1190,42 +1241,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>SUPERSTRADA PER RODI</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>CASCIANI GABRIELE</t>
         </is>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="F18" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="F18" s="12" t="n">
+      <c r="G18" s="12" t="n">
         <v>32</v>
-      </c>
-      <c r="G18" s="12" t="n">
-        <v>1</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I18" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="J18" s="12" t="n">
+      <c r="K18" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="K18" s="12" t="n">
+      <c r="L18" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L18" s="12" t="n">
+      <c r="M18" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="M18" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="N18" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1244,42 +1300,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>SOTTOVIA DUCA DEGLI ABRUZZI</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>Cali Giuseppe</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>RENNA MARCO</t>
         </is>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="F19" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="F19" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="H19" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="12" t="n">
         <v>16</v>
-      </c>
-      <c r="J19" s="12" t="n">
-        <v>2</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>2</v>
       </c>
       <c r="L19" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M19" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="M19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="N19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1298,42 +1359,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>S.S.273 KM. 0+483</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
           <t>Cali Giuseppe</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>CASCIANI GABRIELE</t>
         </is>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="F20" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="F20" s="12" t="n">
+      <c r="G20" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G20" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I20" s="12" t="n">
+      <c r="J20" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="J20" s="12" t="n">
+      <c r="K20" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K20" s="12" t="n">
+      <c r="L20" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="L20" s="12" t="n">
+      <c r="M20" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="M20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="N20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1352,42 +1418,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>SS.7 KM.633+976 S.N.</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
           <t>Cali Giuseppe</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>TESORO DAVIDE</t>
         </is>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="F21" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="F21" s="12" t="n">
+      <c r="G21" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="G21" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H21" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I21" s="12" t="n">
         <v>5</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L21" s="12" t="n">
+      <c r="M21" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="M21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="N21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1406,20 +1477,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>VIALE DI VITTORIO SN</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>Cali Giuseppe</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>CASCIANI GABRIELE</t>
         </is>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="F22" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="F22" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G22" s="12" t="n">
         <v>0</v>
       </c>
@@ -1427,21 +1500,24 @@
         <v>0</v>
       </c>
       <c r="I22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="J22" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="K22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="L22" s="12" t="n">
+      <c r="M22" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="M22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="N22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1460,20 +1536,22 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>SS 16 BIS KM 87+230 NORD</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
           <t>Cali Giuseppe</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>RENNA MARCO</t>
         </is>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="F23" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F23" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G23" s="12" t="n">
         <v>0</v>
       </c>
@@ -1481,21 +1559,24 @@
         <v>0</v>
       </c>
       <c r="I23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J23" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="K23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="M23" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="N23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1512,21 +1593,23 @@
           <t>LUCERA</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr"/>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>VIA FOGGIA S.S. 17 KM. 321+811 SN</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr"/>
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>CASCIANI GABRIELE</t>
         </is>
       </c>
-      <c r="E24" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G24" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H24" s="12" t="n">
         <v>0</v>
       </c>
@@ -1545,7 +1628,10 @@
       <c r="M24" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="N24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>

--- a/docs/files/REPORT_FILTRI/RZV - BRUNI ANGELO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - BRUNI ANGELO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>14</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>602</v>
+        <v>634</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>504</v>
+        <v>531</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,25 +842,25 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>241</v>
+        <v>260</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="I11" s="12" t="n">
         <v>14</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>70</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -901,28 +901,28 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H12" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="J12" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="K12" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="L12" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="I12" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="J12" s="12" t="n">
-        <v>43</v>
-      </c>
-      <c r="K12" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="L12" s="12" t="n">
-        <v>10</v>
-      </c>
       <c r="M12" s="12" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>9</v>
@@ -936,17 +936,17 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>09119</t>
+          <t>09139</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>BARI</t>
+          <t>CASAMASSIMA</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>VIA BITRITTO KM 4+197</t>
+          <t>S.S. 100 KM. 20+123</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -956,56 +956,56 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>RENNA MARCO</t>
+          <t>TESORO DAVIDE</t>
         </is>
       </c>
       <c r="F13" s="12" t="n">
         <v>57</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>09139</t>
+          <t>09119</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CASAMASSIMA</t>
+          <t>BARI</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>S.S. 100 KM. 20+123</t>
+          <t>VIA BITRITTO KM 4+197</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1015,39 +1015,39 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>TESORO DAVIDE</t>
+          <t>RENNA MARCO</t>
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>4</v>
@@ -1090,16 +1090,16 @@
         <v>14</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L15" s="12" t="n">
         <v>21</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>4</v>
@@ -1149,16 +1149,16 @@
         <v>2</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>9</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>0</v>
@@ -1196,22 +1196,22 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L17" s="12" t="n">
         <v>4</v>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1258,7 +1258,7 @@
         <v>18</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>1</v>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1376,7 +1376,7 @@
         <v>15</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>0</v>
@@ -1435,7 +1435,7 @@
         <v>12</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H21" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - BRUNI ANGELO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - BRUNI ANGELO.xlsx
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O24" headerRowCount="1">
-  <autoFilter ref="A10:O24"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O26" headerRowCount="1">
+  <autoFilter ref="A10:O26"/>
   <tableColumns count="15">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:O26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -681,16 +681,16 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>634</v>
+        <v>689</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>531</v>
+        <v>574</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,28 +842,28 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>260</v>
+        <v>282</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="I11" s="12" t="n">
         <v>14</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>250</v>
+        <v>266</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>0</v>
@@ -877,17 +877,17 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>09237</t>
+          <t>09139</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>SAN SEVERO</t>
+          <t>CASAMASSIMA</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>VIA GIUSTINO FORTUNATO SNC</t>
+          <t>S.S. 100 KM. 20+123</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -897,20 +897,20 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>CASCIANI GABRIELE</t>
+          <t>TESORO DAVIDE</t>
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J12" s="12" t="n">
         <v>45</v>
@@ -919,34 +919,34 @@
         <v>15</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>09139</t>
+          <t>09237</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>CASAMASSIMA</t>
+          <t>SAN SEVERO</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>S.S. 100 KM. 20+123</t>
+          <t>VIA GIUSTINO FORTUNATO SNC</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -956,20 +956,20 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>TESORO DAVIDE</t>
+          <t>CASCIANI GABRIELE</t>
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>62</v>
+        <v>103</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J13" s="12" t="n">
         <v>45</v>
@@ -978,17 +978,17 @@
         <v>15</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>30</v>
+        <v>73</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
         <v>57</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H14" s="12" t="n">
         <v>8</v>
@@ -1040,7 +1040,7 @@
         <v>22</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>2</v>
@@ -1078,25 +1078,25 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>38</v>
@@ -1137,28 +1137,28 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I16" s="12" t="n">
         <v>2</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>0</v>
@@ -1196,22 +1196,22 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="I17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="K17" s="12" t="n">
         <v>10</v>
-      </c>
-      <c r="I17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="12" t="n">
-        <v>35</v>
-      </c>
-      <c r="K17" s="12" t="n">
-        <v>9</v>
       </c>
       <c r="L17" s="12" t="n">
         <v>4</v>
@@ -1224,125 +1224,125 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>09267</t>
+          <t>38047</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>LESINA</t>
+          <t>BARI</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>SUPERSTRADA PER RODI</t>
+          <t>SOTTOVIA DUCA DEGLI ABRUZZI</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Cali Giuseppe</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>CASCIANI GABRIELE</t>
+          <t>RENNA MARCO</t>
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>38047</t>
+          <t>09267</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>BARI</t>
+          <t>LESINA</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>SOTTOVIA DUCA DEGLI ABRUZZI</t>
+          <t>SUPERSTRADA PER RODI</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>RENNA MARCO</t>
+          <t>CASCIANI GABRIELE</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="H19" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="K19" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="K19" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="L19" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1376,7 +1376,7 @@
         <v>15</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>0</v>
@@ -1435,13 +1435,13 @@
         <v>12</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="H21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J21" s="12" t="n">
         <v>5</v>
@@ -1467,52 +1467,48 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>09284</t>
+          <t>09285</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>MANFREDONIA</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>VIALE DI VITTORIO SN</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Cali Giuseppe</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr"/>
       <c r="E22" s="2" t="inlineStr">
         <is>
           <t>CASCIANI GABRIELE</t>
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>0</v>
@@ -1526,52 +1522,48 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>54496</t>
+          <t>56298</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>GIOVINAZZO</t>
+          <t>TARANTO</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>SS 16 BIS KM 87+230 NORD</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Cali Giuseppe</t>
-        </is>
-      </c>
+          <t>VL MAGNA GRECIA, 114</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr"/>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>RENNA MARCO</t>
+          <t>TRIFOGLIO DANILO</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>0</v>
@@ -1585,53 +1577,171 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>09284</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>MANFREDONIA</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>VIALE DI VITTORIO SN</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>CASCIANI GABRIELE</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="N24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>Bene</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>54496</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>GIOVINAZZO</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>SS 16 BIS KM 87+230 NORD</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>RENNA MARCO</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="N25" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>Bene</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
           <t>09297</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>LUCERA</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>VIA FOGGIA S.S. 17 KM. 321+811 SN</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr"/>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr"/>
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>CASCIANI GABRIELE</t>
         </is>
       </c>
-      <c r="F24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="12" t="n">
+      <c r="F26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
+      <c r="H26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>

--- a/docs/files/REPORT_FILTRI/RZV - BRUNI ANGELO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - BRUNI ANGELO.xlsx
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O26" headerRowCount="1">
-  <autoFilter ref="A10:O26"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O27" headerRowCount="1">
+  <autoFilter ref="A10:O27"/>
   <tableColumns count="15">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O26"/>
+  <dimension ref="A1:O27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -681,16 +681,16 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>689</v>
+        <v>762</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>574</v>
+        <v>632</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>127</v>
+        <v>165</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,52 +842,52 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>282</v>
+        <v>297</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="I11" s="12" t="n">
         <v>14</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>266</v>
+        <v>281</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="L11" s="12" t="n">
         <v>20</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>09139</t>
+          <t>09237</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>CASAMASSIMA</t>
+          <t>SAN SEVERO</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>S.S. 100 KM. 20+123</t>
+          <t>VIA GIUSTINO FORTUNATO SNC</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -897,56 +897,56 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>TESORO DAVIDE</t>
+          <t>CASCIANI GABRIELE</t>
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>66</v>
+        <v>105</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>09237</t>
+          <t>09139</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>SAN SEVERO</t>
+          <t>CASAMASSIMA</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>VIA GIUSTINO FORTUNATO SNC</t>
+          <t>S.S. 100 KM. 20+123</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -956,46 +956,46 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>CASCIANI GABRIELE</t>
+          <t>TESORO DAVIDE</t>
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>15</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>73</v>
+        <v>33</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>09119</t>
+          <t>54798</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>VIA BITRITTO KM 4+197</t>
+          <t>BRUNO BUOZZI N</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1019,42 +1019,42 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>104</v>
+        <v>74</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>76</v>
+        <v>43</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>54798</t>
+          <t>09119</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>BRUNO BUOZZI N</t>
+          <t>VIA BITRITTO KM 4+197</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1078,31 +1078,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>69</v>
+        <v>108</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L15" s="12" t="n">
         <v>22</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1137,28 +1137,28 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I16" s="12" t="n">
         <v>2</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L16" s="12" t="n">
         <v>10</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>0</v>
@@ -1217,7 +1217,7 @@
         <v>4</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>0</v>
@@ -1231,52 +1231,48 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>38047</t>
+          <t>56298</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>BARI</t>
+          <t>TARANTO</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>SOTTOVIA DUCA DEGLI ABRUZZI</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Cali Giuseppe</t>
-        </is>
-      </c>
+          <t>VL MAGNA GRECIA, 114</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>RENNA MARCO</t>
+          <t>TRIFOGLIO DANILO</t>
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>0</v>
@@ -1290,52 +1286,52 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>09267</t>
+          <t>38047</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>LESINA</t>
+          <t>BARI</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>SUPERSTRADA PER RODI</t>
+          <t>SOTTOVIA DUCA DEGLI ABRUZZI</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Cali Giuseppe</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>CASCIANI GABRIELE</t>
+          <t>RENNA MARCO</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="G19" s="12" t="n">
-        <v>37</v>
-      </c>
-      <c r="H19" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19" s="12" t="n">
-        <v>13</v>
-      </c>
       <c r="K19" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>0</v>
@@ -1349,22 +1345,22 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>09242</t>
+          <t>09267</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI ROTONDO</t>
+          <t>LESINA</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>S.S.273 KM. 0+483</t>
+          <t>SUPERSTRADA PER RODI</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1373,204 +1369,208 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>09424</t>
+          <t>09285</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>MASSAFRA</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>SS.7 KM.633+976 S.N.</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Cali Giuseppe</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr"/>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>TESORO DAVIDE</t>
+          <t>CASCIANI GABRIELE</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>09285</t>
+          <t>09242</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SAN GIOVANNI ROTONDO</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr"/>
+          <t>S.S.273 KM. 0+483</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
           <t>CASCIANI GABRIELE</t>
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>56298</t>
+          <t>09424</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>TARANTO</t>
+          <t>MASSAFRA</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>VL MAGNA GRECIA, 114</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr"/>
+          <t>SS.7 KM.633+976 S.N.</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>TRIFOGLIO DANILO</t>
+          <t>TESORO DAVIDE</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1601,19 +1601,19 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K24" s="12" t="n">
         <v>0</v>
@@ -1636,52 +1636,48 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>54496</t>
+          <t>38033</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>GIOVINAZZO</t>
+          <t>PALAGIANO</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>SS 16 BIS KM 87+230 NORD</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>Cali Giuseppe</t>
-        </is>
-      </c>
+          <t>SS 106 TANGENZIALE PALAGIANO SS 7 AL KM 6+452 S.N</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr"/>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>RENNA MARCO</t>
+          <t>TESORO DAVIDE</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G25" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K25" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="M25" s="12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>0</v>
@@ -1695,53 +1691,112 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>54496</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>GIOVINAZZO</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>SS 16 BIS KM 87+230 NORD</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>RENNA MARCO</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="N26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>Bene</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
           <t>09297</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>LUCERA</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>VIA FOGGIA S.S. 17 KM. 321+811 SN</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr"/>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr"/>
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>CASCIANI GABRIELE</t>
         </is>
       </c>
-      <c r="F26" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="12" t="n">
+      <c r="F27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H26" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
+      <c r="H27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>

--- a/docs/files/REPORT_FILTRI/RZV - BRUNI ANGELO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - BRUNI ANGELO.xlsx
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O27" headerRowCount="1">
-  <autoFilter ref="A10:O27"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O28" headerRowCount="1">
+  <autoFilter ref="A10:O28"/>
   <tableColumns count="15">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O27"/>
+  <dimension ref="A1:O28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -681,16 +681,16 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>762</v>
+        <v>823</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>632</v>
+        <v>687</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>165</v>
+        <v>198</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,28 +842,28 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="L11" s="12" t="n">
         <v>20</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>0</v>
@@ -901,28 +901,28 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="H12" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="I12" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="J12" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="K12" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="L12" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="I12" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="J12" s="12" t="n">
-        <v>48</v>
-      </c>
-      <c r="K12" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="L12" s="12" t="n">
-        <v>13</v>
-      </c>
       <c r="M12" s="12" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>9</v>
@@ -960,10 +960,10 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H13" s="12" t="n">
         <v>7</v>
@@ -972,23 +972,23 @@
         <v>5</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L13" s="12" t="n">
         <v>24</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1019,16 +1019,16 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J14" s="12" t="n">
         <v>37</v>
@@ -1037,7 +1037,7 @@
         <v>5</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>43</v>
@@ -1078,22 +1078,22 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L15" s="12" t="n">
         <v>22</v>
@@ -1137,28 +1137,28 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I16" s="12" t="n">
         <v>2</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L16" s="12" t="n">
         <v>10</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>0</v>
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G17" s="12" t="n">
         <v>0</v>
@@ -1214,7 +1214,7 @@
         <v>10</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>7</v>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1251,87 +1251,83 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>38047</t>
+          <t>09285</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>BARI</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>SOTTOVIA DUCA DEGLI ABRUZZI</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Cali Giuseppe</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr"/>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>RENNA MARCO</t>
+          <t>CASCIANI GABRIELE</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>0</v>
@@ -1345,92 +1341,96 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>09267</t>
+          <t>38047</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>LESINA</t>
+          <t>BARI</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>SUPERSTRADA PER RODI</t>
+          <t>SOTTOVIA DUCA DEGLI ABRUZZI</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Cali Giuseppe</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>CASCIANI GABRIELE</t>
+          <t>RENNA MARCO</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="G20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="G20" s="12" t="n">
-        <v>38</v>
-      </c>
-      <c r="H20" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" s="12" t="n">
-        <v>13</v>
-      </c>
       <c r="K20" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>09285</t>
+          <t>09284</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>MANFREDONIA</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr"/>
+          <t>VIALE DI VITTORIO SN</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
           <t>CASCIANI GABRIELE</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I21" s="12" t="n">
         <v>0</v>
@@ -1439,13 +1439,13 @@
         <v>18</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>0</v>
@@ -1459,22 +1459,22 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>09242</t>
+          <t>09267</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI ROTONDO</t>
+          <t>LESINA</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>S.S.273 KM. 0+483</t>
+          <t>SUPERSTRADA PER RODI</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1483,52 +1483,52 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>09424</t>
+          <t>09242</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>MASSAFRA</t>
+          <t>SAN GIOVANNI ROTONDO</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>SS.7 KM.633+976 S.N.</t>
+          <t>S.S.273 KM. 0+483</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1538,32 +1538,32 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>TESORO DAVIDE</t>
+          <t>CASCIANI GABRIELE</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="G23" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="H23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="J23" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="K23" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="M23" s="12" t="n">
         <v>12</v>
-      </c>
-      <c r="G23" s="12" t="n">
-        <v>61</v>
-      </c>
-      <c r="H23" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="J23" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="K23" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="M23" s="12" t="n">
-        <v>26</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>0</v>
@@ -1577,17 +1577,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>09284</t>
+          <t>09424</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>MANFREDONIA</t>
+          <t>MASSAFRA</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>VIALE DI VITTORIO SN</t>
+          <t>SS.7 KM.633+976 S.N.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1597,39 +1597,39 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>CASCIANI GABRIELE</t>
+          <t>TESORO DAVIDE</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="G24" s="12" t="n">
+        <v>62</v>
+      </c>
+      <c r="H24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="G24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="I24" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J24" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="K24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="M24" s="12" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="N24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G25" s="12" t="n">
         <v>0</v>
@@ -1668,7 +1668,7 @@
         <v>0</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K25" s="12" t="n">
         <v>0</v>
@@ -1797,6 +1797,61 @@
         <v>0</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>Bene</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>09226</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>BRINDISI</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>CIRCONVALLAZIONE</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr"/>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>CANI ANTONIO</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>

--- a/docs/files/REPORT_FILTRI/RZV - BRUNI ANGELO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - BRUNI ANGELO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>18</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>823</v>
+        <v>891</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>687</v>
+        <v>746</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,28 +842,28 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="L11" s="12" t="n">
         <v>20</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>0</v>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I12" s="12" t="n">
         <v>10</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,35 +960,35 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1019,28 +1019,28 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>5</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>0</v>
@@ -1078,19 +1078,19 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I15" s="12" t="n">
         <v>33</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>9</v>
@@ -1137,28 +1137,28 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I16" s="12" t="n">
         <v>2</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>0</v>
@@ -1196,28 +1196,28 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L17" s="12" t="n">
         <v>6</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>0</v>
@@ -1251,35 +1251,35 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="I18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="L18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1306,22 +1306,22 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="G19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="I19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="L19" s="12" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I20" s="12" t="n">
         <v>0</v>
@@ -1383,10 +1383,10 @@
         <v>3</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>0</v>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1545,7 @@
         <v>15</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H23" s="12" t="n">
         <v>0</v>
@@ -1604,7 +1604,7 @@
         <v>12</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H24" s="12" t="n">
         <v>0</v>
@@ -1656,22 +1656,22 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" s="12" t="n">
         <v>1</v>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1750,30 +1750,30 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>09297</t>
+          <t>09226</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>LUCERA</t>
+          <t>BRINDISI</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>VIA FOGGIA S.S. 17 KM. 321+811 SN</t>
+          <t>CIRCONVALLAZIONE</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr"/>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>CASCIANI GABRIELE</t>
+          <t>CANI ANTONIO</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H27" s="12" t="n">
         <v>0</v>
@@ -1782,7 +1782,7 @@
         <v>0</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>0</v>
@@ -1805,30 +1805,30 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>09226</t>
+          <t>09297</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>BRINDISI</t>
+          <t>LUCERA</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>CIRCONVALLAZIONE</t>
+          <t>VIA FOGGIA S.S. 17 KM. 321+811 SN</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>CANI ANTONIO</t>
+          <t>CASCIANI GABRIELE</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H28" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - BRUNI ANGELO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - BRUNI ANGELO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>18</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>891</v>
+        <v>954</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>746</v>
+        <v>804</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>226</v>
+        <v>252</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,35 +842,35 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="L11" s="12" t="n">
         <v>20</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -901,35 +901,35 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L12" s="12" t="n">
         <v>16</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
         <v>75</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H13" s="12" t="n">
         <v>10</v>
@@ -981,14 +981,14 @@
         <v>27</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>17</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1019,28 +1019,28 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>5</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>0</v>
@@ -1078,19 +1078,19 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I15" s="12" t="n">
         <v>33</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>9</v>
@@ -1099,7 +1099,7 @@
         <v>22</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>2</v>
@@ -1137,10 +1137,10 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>12</v>
@@ -1149,16 +1149,16 @@
         <v>2</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>13</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>0</v>
@@ -1217,14 +1217,14 @@
         <v>6</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1251,25 +1251,25 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>2</v>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1306,22 +1306,22 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L19" s="12" t="n">
         <v>0</v>
@@ -1334,24 +1334,24 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>38047</t>
+          <t>09284</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>BARI</t>
+          <t>MANFREDONIA</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>SOTTOVIA DUCA DEGLI ABRUZZI</t>
+          <t>VIALE DI VITTORIO SN</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1361,32 +1361,32 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>RENNA MARCO</t>
+          <t>CASCIANI GABRIELE</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H20" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="I20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="K20" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="K20" s="12" t="n">
-        <v>3</v>
-      </c>
       <c r="L20" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>0</v>
@@ -1400,17 +1400,17 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>09284</t>
+          <t>38047</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>MANFREDONIA</t>
+          <t>BARI</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>VIALE DI VITTORIO SN</t>
+          <t>SOTTOVIA DUCA DEGLI ABRUZZI</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1420,32 +1420,32 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>CASCIANI GABRIELE</t>
+          <t>RENNA MARCO</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="G21" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="I21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="12" t="n">
         <v>19</v>
-      </c>
-      <c r="G21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="I21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="12" t="n">
-        <v>18</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>3</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>0</v>
@@ -1518,76 +1518,72 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>09242</t>
+          <t>38033</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI ROTONDO</t>
+          <t>PALAGIANO</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>S.S.273 KM. 0+483</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Cali Giuseppe</t>
-        </is>
-      </c>
+          <t>SS 106 TANGENZIALE PALAGIANO SS 7 AL KM 6+452 S.N</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr"/>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>CASCIANI GABRIELE</t>
+          <t>TESORO DAVIDE</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="G23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="G23" s="12" t="n">
-        <v>39</v>
-      </c>
-      <c r="H23" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="J23" s="12" t="n">
-        <v>11</v>
-      </c>
       <c r="K23" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L23" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="L23" s="12" t="n">
-        <v>5</v>
-      </c>
       <c r="M23" s="12" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>09424</t>
+          <t>09242</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>MASSAFRA</t>
+          <t>SAN GIOVANNI ROTONDO</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>SS.7 KM.633+976 S.N.</t>
+          <t>S.S.273 KM. 0+483</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1597,32 +1593,32 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>TESORO DAVIDE</t>
+          <t>CASCIANI GABRIELE</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="G24" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="H24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="J24" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="K24" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="M24" s="12" t="n">
         <v>12</v>
-      </c>
-      <c r="G24" s="12" t="n">
-        <v>64</v>
-      </c>
-      <c r="H24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="J24" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="K24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="M24" s="12" t="n">
-        <v>26</v>
       </c>
       <c r="N24" s="12" t="n">
         <v>0</v>
@@ -1636,107 +1632,107 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>38033</t>
+          <t>09424</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>PALAGIANO</t>
+          <t>MASSAFRA</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>SS 106 TANGENZIALE PALAGIANO SS 7 AL KM 6+452 S.N</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr"/>
+          <t>SS.7 KM.633+976 S.N.</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
           <t>TESORO DAVIDE</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="G25" s="12" t="n">
+        <v>68</v>
+      </c>
+      <c r="H25" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="G25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J25" s="12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>54496</t>
+          <t>09226</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>GIOVINAZZO</t>
+          <t>BRINDISI</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>SS 16 BIS KM 87+230 NORD</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Cali Giuseppe</t>
-        </is>
-      </c>
+          <t>CIRCONVALLAZIONE</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr"/>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>RENNA MARCO</t>
+          <t>CANI ANTONIO</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>0</v>
@@ -1750,23 +1746,27 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>09226</t>
+          <t>54496</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>BRINDISI</t>
+          <t>GIOVINAZZO</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>CIRCONVALLAZIONE</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr"/>
+          <t>SS 16 BIS KM 87+230 NORD</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>CANI ANTONIO</t>
+          <t>RENNA MARCO</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
@@ -1791,7 +1791,7 @@
         <v>0</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - BRUNI ANGELO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - BRUNI ANGELO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W25</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>18</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>954</v>
+        <v>1016</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>804</v>
+        <v>859</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,35 +842,35 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I11" s="12" t="n">
         <v>17</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="L11" s="12" t="n">
         <v>20</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -901,28 +901,28 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="I12" s="12" t="n">
         <v>11</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>11</v>
@@ -936,17 +936,17 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>09139</t>
+          <t>54798</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>CASAMASSIMA</t>
+          <t>BARI</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>S.S. 100 KM. 20+123</t>
+          <t>BRUNO BUOZZI N</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -956,35 +956,35 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>TESORO DAVIDE</t>
+          <t>RENNA MARCO</t>
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -995,17 +995,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>54798</t>
+          <t>09139</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>BARI</t>
+          <t>CASAMASSIMA</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>BRUNO BUOZZI N</t>
+          <t>S.S. 100 KM. 20+123</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1015,39 +1015,39 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>RENNA MARCO</t>
+          <t>TESORO DAVIDE</t>
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="H14" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="I14" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="J14" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="K14" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="L14" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="I14" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="J14" s="12" t="n">
-        <v>41</v>
-      </c>
-      <c r="K14" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="L14" s="12" t="n">
-        <v>38</v>
-      </c>
       <c r="M14" s="12" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1078,19 +1078,19 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>12</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>9</v>
@@ -1099,7 +1099,7 @@
         <v>22</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>2</v>
@@ -1140,13 +1140,13 @@
         <v>64</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>12</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J16" s="12" t="n">
         <v>55</v>
@@ -1158,7 +1158,7 @@
         <v>13</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>0</v>
@@ -1196,35 +1196,35 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1251,35 +1251,35 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="L18" s="12" t="n">
         <v>1</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1306,22 +1306,22 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="G19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L19" s="12" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L20" s="12" t="n">
         <v>1</v>
@@ -1393,7 +1393,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1445,14 +1445,14 @@
         <v>3</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
         <v>19</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H22" s="12" t="n">
         <v>1</v>
@@ -1538,7 +1538,7 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G23" s="12" t="n">
         <v>0</v>
@@ -1550,23 +1550,23 @@
         <v>0</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L23" s="12" t="n">
         <v>1</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1600,7 @@
         <v>15</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="H24" s="12" t="n">
         <v>0</v>
@@ -1711,7 +1711,7 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G26" s="12" t="n">
         <v>0</v>
@@ -1729,17 +1729,17 @@
         <v>2</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/RZV - BRUNI ANGELO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - BRUNI ANGELO.xlsx
@@ -684,13 +684,13 @@
         <v>18</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1016</v>
+        <v>1031</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>859</v>
+        <v>0</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,19 +842,19 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="G11" s="12" t="n">
         <v>79</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I11" s="12" t="n">
         <v>17</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>121</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G12" s="12" t="n">
         <v>132</v>
@@ -913,7 +913,7 @@
         <v>11</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>38</v>
@@ -922,7 +922,7 @@
         <v>18</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>11</v>
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="G13" s="12" t="n">
         <v>96</v>
@@ -972,7 +972,7 @@
         <v>24</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>5</v>
@@ -981,7 +981,7 @@
         <v>41</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>0</v>
@@ -1019,10 +1019,10 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H14" s="12" t="n">
         <v>11</v>
@@ -1031,7 +1031,7 @@
         <v>6</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>20</v>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>12</v>
@@ -1090,7 +1090,7 @@
         <v>35</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>9</v>
@@ -1137,10 +1137,10 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>12</v>
@@ -1149,7 +1149,7 @@
         <v>3</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>13</v>
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G17" s="12" t="n">
         <v>3</v>
@@ -1208,7 +1208,7 @@
         <v>3</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>17</v>
@@ -1263,7 +1263,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>27</v>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>23</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K20" s="12" t="n">
         <v>7</v>
@@ -1386,14 +1386,14 @@
         <v>1</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G21" s="12" t="n">
         <v>1</v>
@@ -1436,7 +1436,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>3</v>
@@ -1445,14 +1445,14 @@
         <v>3</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
         <v>19</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H22" s="12" t="n">
         <v>1</v>
@@ -1495,7 +1495,7 @@
         <v>1</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K22" s="12" t="n">
         <v>4</v>
@@ -1504,14 +1504,14 @@
         <v>6</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1550,7 @@
         <v>0</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>5</v>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1597,19 +1597,19 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K24" s="12" t="n">
         <v>1</v>
@@ -1656,10 +1656,10 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H25" s="12" t="n">
         <v>0</v>
@@ -1668,7 +1668,7 @@
         <v>8</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K25" s="12" t="n">
         <v>0</v>
@@ -1677,7 +1677,7 @@
         <v>6</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
         <v>0</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K26" s="12" t="n">
         <v>2</v>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1782,7 +1782,7 @@
         <v>0</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>0</v>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1828,7 @@
         <v>0</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H28" s="12" t="n">
         <v>0</v>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
